--- a/frontend/public/import-template.xlsx
+++ b/frontend/public/import-template.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1100100200001</t>
+          <t>1100100200009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1100100200001</t>
+          <t>1100100200009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1100100200001</t>
+          <t>1100100200009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1100100200001</t>
+          <t>1100100200009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
